--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -65,7 +65,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
   </si>
   <si>
-    <t>dateTimeĵ</t>
+    <t>dateTimeĵ, Periodĵ</t>
   </si>
   <si>
     <t>Quantityĵ, CodeableConceptĵ, Rangeĵ, Ratioĵ</t>
